--- a/artfynd/A 52030-2025 artfynd.xlsx
+++ b/artfynd/A 52030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111817582</v>
       </c>
       <c r="B2" t="n">
-        <v>88283</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119300356</v>
+        <v>119300340</v>
       </c>
       <c r="B3" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578403</v>
+        <v>578394</v>
       </c>
       <c r="R3" t="n">
-        <v>6398854</v>
+        <v>6398753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +886,342 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111817611</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 718 m fl, Sälden, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578480</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398699</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Relativt tunn asp.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119300290</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 781, Sälden, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>578582</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398691</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119300356</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 781, Sälden, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>578403</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398854</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
